--- a/artfynd/A 5556-2023 artfynd.xlsx
+++ b/artfynd/A 5556-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 5556-2023 artfynd.xlsx
+++ b/artfynd/A 5556-2023 artfynd.xlsx
@@ -925,11 +925,11 @@
         <v>116167453</v>
       </c>
       <c r="B4" t="n">
-        <v>58077</v>
+        <v>58337</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">

--- a/artfynd/A 5556-2023 artfynd.xlsx
+++ b/artfynd/A 5556-2023 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>116167453</v>
       </c>
       <c r="B4" t="n">
-        <v>58337</v>
+        <v>58340</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 5556-2023 artfynd.xlsx
+++ b/artfynd/A 5556-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>568336</v>
       </c>
       <c r="B2" t="n">
-        <v>101308</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104232</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542740.4208212423</v>
+        <v>542740</v>
       </c>
       <c r="R2" t="n">
-        <v>6214923.177536017</v>
+        <v>6214923</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +752,9 @@
           <t>2011-07-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-07-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,12 +789,7 @@
         <v>99634645</v>
       </c>
       <c r="B3" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -849,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542746.6100131997</v>
+        <v>542747</v>
       </c>
       <c r="R3" t="n">
-        <v>6214919.333049304</v>
+        <v>6214919</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -882,19 +862,9 @@
           <t>2022-04-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-04-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,16 +895,11 @@
         <v>116167453</v>
       </c>
       <c r="B4" t="n">
-        <v>58340</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>58816</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">

--- a/artfynd/A 5556-2023 artfynd.xlsx
+++ b/artfynd/A 5556-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/568336</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99634645</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,8 +1020,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116167453</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>